--- a/Test Scenarios Axis Bank.xlsx
+++ b/Test Scenarios Axis Bank.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13da4701092726d5/Testing/Axis Bank/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="8_{6E6E5CFB-C9A8-4B8E-B9EA-DD8F248CF15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{483F3DD9-41EA-4EBF-A320-9F6D9EBBCA1F}"/>
+  <xr:revisionPtr revIDLastSave="427" documentId="8_{6E6E5CFB-C9A8-4B8E-B9EA-DD8F248CF15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CD4F681-63DA-4E41-81E2-9D9B2A9E9702}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{836B0E2C-C0D6-4FF2-BA15-7D3C41907B1D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{836B0E2C-C0D6-4FF2-BA15-7D3C41907B1D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Scenario" sheetId="2" r:id="rId1"/>
+    <sheet name="Version History" sheetId="3" r:id="rId1"/>
+    <sheet name="Test Scenario" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="114">
   <si>
     <t>Project Name</t>
   </si>
@@ -361,13 +362,28 @@
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Version History</t>
+  </si>
+  <si>
+    <t>Axis Bank Home Page Testing</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>FRS – Axis Bank Home Page (www.axisbank.com)</t>
+  </si>
+  <si>
+    <t>Dhananjay Gharad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,8 +404,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -405,6 +441,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,11 +508,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -485,6 +530,20 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -823,8 +882,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8098CA2-8D81-4E91-B232-09A40382362A}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.21875" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7383F14D-F942-43FE-BB48-8005878BB811}">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.88671875" customWidth="1"/>
@@ -833,783 +1023,752 @@
     <col min="5" max="5" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="5" t="s">
+    <row r="11" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5">
         <v>7</v>
       </c>
-      <c r="D8" s="5" t="s">
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5">
         <v>8</v>
       </c>
-      <c r="E8" s="5" t="s">
+    </row>
+    <row r="14" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6">
+    <row r="17" spans="1:5" s="2" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="6">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="6">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="3" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="2"/>
-      <c r="E29" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="7">
-        <v>6</v>
-      </c>
-    </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D51" s="2"/>
-      <c r="E51" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="2"/>
-      <c r="E52" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D53" s="2"/>
-      <c r="E53" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D54" s="2"/>
-      <c r="E54" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D55" s="2"/>
-      <c r="E55" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="2"/>
-      <c r="E56" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="10" t="s">
+      <c r="A50" s="7"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="2">
-        <f>SUM(E9:E56)</f>
+      <c r="D50" s="8"/>
+      <c r="E50" s="1">
+        <f>SUM(E2:E49)</f>
         <v>337</v>
       </c>
     </row>
